--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103528</v>
+        <v>103700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103700</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103755</v>
+        <v>103762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103762</v>
+        <v>103765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103765</v>
+        <v>103769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43454-2019 artfynd.xlsx
+++ b/artfynd/A 43454-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125473481</v>
       </c>
       <c r="B2" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
